--- a/docs/软件开发项目计划-预维护平台.xlsx
+++ b/docs/软件开发项目计划-预维护平台.xlsx
@@ -5,19 +5,20 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://siemens.sharepoint.com/teams/RG-CNDICSDCPSMDIG-InternalProjects/Shared Documents/202512_维护服务平台/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\28_IT_Projects\3_Web\NewISP\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1397" documentId="11_AD4DB114E441178AC67DF4636E53E588693EDF3F" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A8F92DD6-1EF6-40DC-A967-2CCFC94761FE}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93B4A20B-387D-4D86-A257-1A0617223482}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="571" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="571" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
     <sheet name="WBS" sheetId="2" r:id="rId2"/>
-    <sheet name="Time Plan" sheetId="3" r:id="rId3"/>
-    <sheet name="架构设计" sheetId="4" r:id="rId4"/>
-    <sheet name="minutes" sheetId="6" r:id="rId5"/>
+    <sheet name="功能需求" sheetId="7" r:id="rId3"/>
+    <sheet name="Time Plan" sheetId="3" r:id="rId4"/>
+    <sheet name="架构设计" sheetId="4" r:id="rId5"/>
+    <sheet name="minutes" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="117">
   <si>
     <t>合同号 
 Contract No：</t>
@@ -303,6 +304,121 @@
   <si>
     <t>测试环境搭建</t>
   </si>
+  <si>
+    <t>离线数据采集</t>
+  </si>
+  <si>
+    <t>在线获取任务</t>
+  </si>
+  <si>
+    <t>云端同步</t>
+  </si>
+  <si>
+    <t>报告生成</t>
+  </si>
+  <si>
+    <t>报告渲染</t>
+  </si>
+  <si>
+    <t>报告编辑打印</t>
+  </si>
+  <si>
+    <t>模块名称</t>
+  </si>
+  <si>
+    <t>描述</t>
+  </si>
+  <si>
+    <t>Web端核心功能</t>
+  </si>
+  <si>
+    <t>客户设备管理，包括客户信息和设备信息等</t>
+  </si>
+  <si>
+    <t>维护项目管理，包括创建项目，方案匹配等</t>
+  </si>
+  <si>
+    <t>维护方案管理，包括创建不同类别的维护方案等</t>
+  </si>
+  <si>
+    <t>报告管理模块，包括生成报告，导出报告和上传报告</t>
+  </si>
+  <si>
+    <t>移动端核心功能</t>
+  </si>
+  <si>
+    <t>维护任务同步</t>
+  </si>
+  <si>
+    <t>维护数据表单录入，规则校验</t>
+  </si>
+  <si>
+    <t>数据本地存储与上传</t>
+  </si>
+  <si>
+    <t>基础功能</t>
+  </si>
+  <si>
+    <t>开发和测试环境搭建</t>
+  </si>
+  <si>
+    <t>登录鉴权，角色权限等</t>
+  </si>
+  <si>
+    <t>配置管理，如设备配置，报告配置、规则配置等</t>
+  </si>
+  <si>
+    <t>需求澄清与设计</t>
+  </si>
+  <si>
+    <t>基于需求沟通原型设计</t>
+  </si>
+  <si>
+    <t>报告模版沟通与设计</t>
+  </si>
+  <si>
+    <t>报告生成规则梳理和呈现</t>
+  </si>
+  <si>
+    <t>部署与调试</t>
+  </si>
+  <si>
+    <t>打包与部署</t>
+  </si>
+  <si>
+    <t>调试与测试</t>
+  </si>
+  <si>
+    <t>Bug修复与迭代</t>
+  </si>
+  <si>
+    <t>总天数</t>
+  </si>
+  <si>
+    <t>场景及测试</t>
+  </si>
+  <si>
+    <t>主任工程师可以创建客户信息及客户的设备信息；支持批量上传和导出数据</t>
+  </si>
+  <si>
+    <t>主任工程师可以创建项目，编辑项目信息，调整维护方案</t>
+  </si>
+  <si>
+    <t>主任工程师可以创建和维护方案</t>
+  </si>
+  <si>
+    <t>1，维护任务全部完成后，即所有维护数据全部OK后，自动生成报告；
+2，生成报告后，主任工程师可以导出报告及编辑报告，生成最终版的报告后可以关闭项目</t>
+  </si>
+  <si>
+    <t>执行工程师可以通过pad同步云端项目任务数据</t>
+  </si>
+  <si>
+    <t>执行工程师完成每个任务后，可以将数据同步到云端，数据在本地也会存储。</t>
+  </si>
+  <si>
+    <t>执行工程师可以离线为每个人物录入现场数据，包括拍照上传，并且可以实时看到检测是否合格，如进行了维护处理，并可以进行再次检测。</t>
+  </si>
 </sst>
 </file>
 
@@ -311,7 +427,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd;@"/>
   </numFmts>
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -368,8 +484,21 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Siemens Sans Global"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Siemens Sans Global"/>
+      <charset val="134"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -400,8 +529,20 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE2EFDA"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="6">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -470,12 +611,49 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="62">
+  <cellXfs count="71">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
@@ -621,6 +799,33 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -779,7 +984,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0</c:v>
+                  <c:v>46122</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>0</c:v>
@@ -797,7 +1002,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0</c:v>
+                  <c:v>46136</c:v>
                 </c:pt>
                 <c:pt idx="12">
                   <c:v>0</c:v>
@@ -812,7 +1017,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>0</c:v>
+                  <c:v>46146</c:v>
                 </c:pt>
                 <c:pt idx="17">
                   <c:v>0</c:v>
@@ -939,7 +1144,7 @@
                 <c:formatCode>0</c:formatCode>
                 <c:ptCount val="22"/>
                 <c:pt idx="0">
-                  <c:v>15</c:v>
+                  <c:v>9</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>0</c:v>
@@ -954,7 +1159,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0</c:v>
+                  <c:v>14</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>0</c:v>
@@ -972,7 +1177,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0</c:v>
+                  <c:v>10</c:v>
                 </c:pt>
                 <c:pt idx="12">
                   <c:v>0</c:v>
@@ -987,7 +1192,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>0</c:v>
+                  <c:v>14</c:v>
                 </c:pt>
                 <c:pt idx="17">
                   <c:v>0</c:v>
@@ -1690,11 +1895,11 @@
         <v>46113</v>
       </c>
       <c r="I7" s="37">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="J7" s="35">
         <f>IF(WBS!H7="","",H7+I7)</f>
-        <v>46128</v>
+        <v>46122</v>
       </c>
       <c r="K7" s="37"/>
       <c r="L7" s="37"/>
@@ -1865,11 +2070,16 @@
         <f t="shared" si="0"/>
         <v>sprint-2 完成项目创建-</v>
       </c>
-      <c r="H14" s="35"/>
-      <c r="I14" s="33"/>
-      <c r="J14" s="35" t="str">
+      <c r="H14" s="35">
+        <f>J7</f>
+        <v>46122</v>
+      </c>
+      <c r="I14" s="33">
+        <v>14</v>
+      </c>
+      <c r="J14" s="35">
         <f>IF(WBS!H14="","",H14+I14)</f>
-        <v/>
+        <v>46136</v>
       </c>
       <c r="K14" s="33"/>
       <c r="L14" s="36"/>
@@ -1971,18 +2181,25 @@
         <f t="shared" si="0"/>
         <v>sprint-3 移动端操作接口-</v>
       </c>
-      <c r="H20" s="34"/>
-      <c r="I20" s="33"/>
-      <c r="J20" s="35" t="str">
+      <c r="H20" s="34">
+        <f>J14</f>
+        <v>46136</v>
+      </c>
+      <c r="I20" s="33">
+        <v>10</v>
+      </c>
+      <c r="J20" s="35">
         <f>IF(WBS!H20="","",H20+I20)</f>
-        <v/>
+        <v>46146</v>
       </c>
       <c r="K20" s="33"/>
       <c r="L20" s="36"/>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21" s="40"/>
-      <c r="B21" s="5"/>
+      <c r="B21" s="5" t="s">
+        <v>80</v>
+      </c>
       <c r="C21" s="6"/>
       <c r="D21" s="5"/>
       <c r="E21" s="7"/>
@@ -1996,7 +2213,9 @@
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A22" s="40"/>
-      <c r="B22" s="5"/>
+      <c r="B22" s="5" t="s">
+        <v>79</v>
+      </c>
       <c r="C22" s="6"/>
       <c r="D22" s="5"/>
       <c r="E22" s="7"/>
@@ -2010,7 +2229,9 @@
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23" s="40"/>
-      <c r="B23" s="5"/>
+      <c r="B23" s="5" t="s">
+        <v>81</v>
+      </c>
       <c r="C23" s="6"/>
       <c r="D23" s="5"/>
       <c r="E23" s="7"/>
@@ -2051,18 +2272,25 @@
         <f t="shared" si="0"/>
         <v>sprint-4 报告生成-</v>
       </c>
-      <c r="H25" s="34"/>
-      <c r="I25" s="33"/>
-      <c r="J25" s="35" t="str">
+      <c r="H25" s="34">
+        <f>J20</f>
+        <v>46146</v>
+      </c>
+      <c r="I25" s="33">
+        <v>14</v>
+      </c>
+      <c r="J25" s="35">
         <f>IF(WBS!H25="","",H25+I25)</f>
-        <v/>
+        <v>46160</v>
       </c>
       <c r="K25" s="33"/>
       <c r="L25" s="36"/>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26" s="40"/>
-      <c r="B26" s="8"/>
+      <c r="B26" s="8" t="s">
+        <v>82</v>
+      </c>
       <c r="C26" s="6"/>
       <c r="D26" s="5"/>
       <c r="E26" s="7"/>
@@ -2076,7 +2304,9 @@
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A27" s="40"/>
-      <c r="B27" s="8"/>
+      <c r="B27" s="8" t="s">
+        <v>83</v>
+      </c>
       <c r="C27" s="6"/>
       <c r="D27" s="5"/>
       <c r="E27" s="7"/>
@@ -2090,7 +2320,9 @@
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A28" s="40"/>
-      <c r="B28" s="8"/>
+      <c r="B28" s="8" t="s">
+        <v>84</v>
+      </c>
       <c r="C28" s="6"/>
       <c r="D28" s="5"/>
       <c r="E28" s="7"/>
@@ -2296,6 +2528,182 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C0C93AF3-4CE3-4BEC-A0EC-9F66855EE8D3}">
+  <dimension ref="A1:C18"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="19.85546875" customWidth="1"/>
+    <col min="2" max="2" width="33.28515625" style="45" customWidth="1"/>
+    <col min="3" max="3" width="48.85546875" style="45" customWidth="1"/>
+    <col min="4" max="4" width="24.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="66" t="s">
+        <v>85</v>
+      </c>
+      <c r="B1" s="64" t="s">
+        <v>86</v>
+      </c>
+      <c r="C1" s="47" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A2" s="68" t="s">
+        <v>87</v>
+      </c>
+      <c r="B2" s="65" t="s">
+        <v>88</v>
+      </c>
+      <c r="C2" s="47" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A3" s="69"/>
+      <c r="B3" s="65" t="s">
+        <v>90</v>
+      </c>
+      <c r="C3" s="47" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A4" s="69"/>
+      <c r="B4" s="65" t="s">
+        <v>89</v>
+      </c>
+      <c r="C4" s="47" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="60" x14ac:dyDescent="0.25">
+      <c r="A5" s="70"/>
+      <c r="B5" s="65" t="s">
+        <v>91</v>
+      </c>
+      <c r="C5" s="47" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="67" t="s">
+        <v>92</v>
+      </c>
+      <c r="B6" s="63" t="s">
+        <v>93</v>
+      </c>
+      <c r="C6" s="47" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A7" s="62"/>
+      <c r="B7" s="63" t="s">
+        <v>94</v>
+      </c>
+      <c r="C7" s="47" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A8" s="62"/>
+      <c r="B8" s="63" t="s">
+        <v>95</v>
+      </c>
+      <c r="C8" s="47" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" s="62" t="s">
+        <v>96</v>
+      </c>
+      <c r="B9" s="63" t="s">
+        <v>97</v>
+      </c>
+      <c r="C9" s="47"/>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" s="62"/>
+      <c r="B10" s="63" t="s">
+        <v>98</v>
+      </c>
+      <c r="C10" s="47"/>
+    </row>
+    <row r="11" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A11" s="62"/>
+      <c r="B11" s="63" t="s">
+        <v>99</v>
+      </c>
+      <c r="C11" s="47"/>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" s="62" t="s">
+        <v>100</v>
+      </c>
+      <c r="B12" s="63" t="s">
+        <v>101</v>
+      </c>
+      <c r="C12" s="47"/>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" s="62"/>
+      <c r="B13" s="63" t="s">
+        <v>102</v>
+      </c>
+      <c r="C13" s="47"/>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" s="62"/>
+      <c r="B14" s="63" t="s">
+        <v>103</v>
+      </c>
+      <c r="C14" s="47"/>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" s="62" t="s">
+        <v>104</v>
+      </c>
+      <c r="B15" s="63" t="s">
+        <v>105</v>
+      </c>
+      <c r="C15" s="47"/>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" s="62"/>
+      <c r="B16" s="63" t="s">
+        <v>106</v>
+      </c>
+      <c r="C16" s="47"/>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" s="62"/>
+      <c r="B17" s="63" t="s">
+        <v>107</v>
+      </c>
+      <c r="C17" s="47"/>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" s="18"/>
+      <c r="B18" s="63" t="s">
+        <v>108</v>
+      </c>
+      <c r="C18" s="47"/>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A6:A8"/>
+    <mergeCell ref="A9:A11"/>
+    <mergeCell ref="A12:A14"/>
+    <mergeCell ref="A15:A17"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F52694BD-E348-4AF0-ADF4-5A74659CC7E7}">
   <dimension ref="A1:N27"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
@@ -2352,11 +2760,11 @@
       </c>
       <c r="C2" s="23">
         <f>IF(WBS!I7="","",WBS!I7)</f>
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="D2" s="7">
         <f>IF(WBS!I7="","",B2+C2)</f>
-        <v>46128</v>
+        <v>46122</v>
       </c>
       <c r="G2" s="21"/>
       <c r="N2" s="22"/>
@@ -2438,17 +2846,17 @@
         <f>IF(WBS!G14="-","",WBS!G14)</f>
         <v>sprint-2 完成项目创建-</v>
       </c>
-      <c r="B7" s="7" t="str">
+      <c r="B7" s="7">
         <f>IF(WBS!H14="","",WBS!H14)</f>
-        <v/>
-      </c>
-      <c r="C7" s="23" t="str">
+        <v>46122</v>
+      </c>
+      <c r="C7" s="23">
         <f>IF(WBS!I14="","",WBS!I14)</f>
-        <v/>
-      </c>
-      <c r="D7" s="7" t="str">
+        <v>14</v>
+      </c>
+      <c r="D7" s="7">
         <f>IF(WBS!I14="","",B7+C7)</f>
-        <v/>
+        <v>46136</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
@@ -2546,17 +2954,17 @@
         <f>IF(WBS!G20="-","",WBS!G20)</f>
         <v>sprint-3 移动端操作接口-</v>
       </c>
-      <c r="B13" s="7" t="str">
+      <c r="B13" s="7">
         <f>IF(WBS!H20="","",WBS!H20)</f>
-        <v/>
-      </c>
-      <c r="C13" s="23" t="str">
+        <v>46136</v>
+      </c>
+      <c r="C13" s="23">
         <f>IF(WBS!I20="","",WBS!I20)</f>
-        <v/>
-      </c>
-      <c r="D13" s="7" t="str">
+        <v>10</v>
+      </c>
+      <c r="D13" s="7">
         <f>IF(WBS!I20="","",B13+C13)</f>
-        <v/>
+        <v>46146</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
@@ -2636,17 +3044,17 @@
         <f>IF(WBS!G25="-","",WBS!G25)</f>
         <v>sprint-4 报告生成-</v>
       </c>
-      <c r="B18" s="7" t="str">
+      <c r="B18" s="7">
         <f>IF(WBS!H25="","",WBS!H25)</f>
-        <v/>
-      </c>
-      <c r="C18" s="23" t="str">
+        <v>46146</v>
+      </c>
+      <c r="C18" s="23">
         <f>IF(WBS!I25="","",WBS!I25)</f>
-        <v/>
-      </c>
-      <c r="D18" s="7" t="str">
+        <v>14</v>
+      </c>
+      <c r="D18" s="7">
         <f>IF(WBS!I25="","",B18+C18)</f>
-        <v/>
+        <v>46160</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -2782,7 +3190,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B824078-81F8-4512-9F98-369AFF495167}">
   <dimension ref="A1:E29"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2973,7 +3381,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{737133D5-5A2B-4847-89A8-78E1DEF8DAC9}">
   <dimension ref="A1:E9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -3288,6 +3696,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="6bd1f968-35b2-42cf-8f7c-e2953acad71e">
@@ -3295,15 +3712,6 @@
     </lcf76f155ced4ddcb4097134ff3c332f>
   </documentManagement>
 </p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3326,6 +3734,14 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D0F0BDBA-B25F-4B13-9129-7AFFFECE8FC2}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{405780F8-7536-4E8F-AE43-2ECD1E074F9C}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -3335,14 +3751,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D0F0BDBA-B25F-4B13-9129-7AFFFECE8FC2}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{9d258917-277f-42cd-a3cd-14c4e9ee58bc}" enabled="1" method="Standard" siteId="{38ae3bcd-9579-4fd4-adda-b42e1495d55a}" removed="0"/>
